--- a/data/master_armada.xlsx
+++ b/data/master_armada.xlsx
@@ -1,40 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Jenis_Armada</t>
+  </si>
+  <si>
+    <t>Max_Volume_m3</t>
+  </si>
+  <si>
+    <t>Max_Tonase_Kg</t>
+  </si>
+  <si>
+    <t>Safety_Factor</t>
+  </si>
+  <si>
+    <t>Length_cm</t>
+  </si>
+  <si>
+    <t>Height_cm</t>
+  </si>
+  <si>
+    <t>Width_cm</t>
+  </si>
+  <si>
+    <t>Engkel</t>
+  </si>
+  <si>
+    <t>CDE</t>
+  </si>
+  <si>
+    <t>Fuso</t>
+  </si>
+  <si>
+    <t>Tronton</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +86,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,152 +403,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Jenis_Armada</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Max_Volume_m3</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Max_Tonase_Kg</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Safety_Factor</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Length_cm</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Height_cm</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Width_cm</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Engkel</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
         <v>8</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2500</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>300</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>180</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>200</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CDE</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
         <v>15</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>5000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>500</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>220</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fuso</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>25</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>8000</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>700</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>220</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>240</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tronton</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
         <v>40</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>15000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>900</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>240</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070E3D72CCA08644087C9FCADB1718278" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1cc8d91cc763930dc5d15b577ed7a101">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0886a85-e68e-4b42-8edb-c639a7945b69" xmlns:ns3="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6db848d96a87503e65ee1d4dfcdbf9d1" ns2:_="" ns3:_="">
+    <xsd:import namespace="b0886a85-e68e-4b42-8edb-c639a7945b69"/>
+    <xsd:import namespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b0886a85-e68e-4b42-8edb-c639a7945b69" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d90de106-bb39-41f4-915c-b71cc21c8f62" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cbd141ff-a5ff-442b-83f9-b2cf40ba1a7d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d44dd7a7-1c38-4d96-9b4d-61cfd733981b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0886a85-e68e-4b42-8edb-c639a7945b69">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24D4AD04-4C36-4B63-8AAB-D3BCEDBE65D6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08BD9DD0-813B-4C15-9967-09ED91497EC5}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E829B677-1520-4805-8F08-F8100DE78CF2}"/>
 </file>
--- a/data/master_armada.xlsx
+++ b/data/master_armada.xlsx
@@ -14,11 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Jenis_Armada</t>
   </si>
   <si>
+    <t>Length_cm</t>
+  </si>
+  <si>
+    <t>Width_cm</t>
+  </si>
+  <si>
+    <t>Height_cm</t>
+  </si>
+  <si>
     <t>Max_Volume_m3</t>
   </si>
   <si>
@@ -28,25 +37,40 @@
     <t>Safety_Factor</t>
   </si>
   <si>
-    <t>Length_cm</t>
-  </si>
-  <si>
-    <t>Height_cm</t>
-  </si>
-  <si>
-    <t>Width_cm</t>
-  </si>
-  <si>
-    <t>Engkel</t>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>BUILD UP</t>
+  </si>
+  <si>
+    <t>BUILD UP 20</t>
+  </si>
+  <si>
+    <t>FUSO (SUMATERA)</t>
+  </si>
+  <si>
+    <t>CONTAINER 20</t>
+  </si>
+  <si>
+    <t>TRONTON</t>
+  </si>
+  <si>
+    <t>ENGKEL</t>
+  </si>
+  <si>
+    <t>CDD LONG</t>
+  </si>
+  <si>
+    <t>DUTRO</t>
+  </si>
+  <si>
+    <t>CDD</t>
   </si>
   <si>
     <t>CDE</t>
   </si>
   <si>
-    <t>Fuso</t>
-  </si>
-  <si>
-    <t>Tronton</t>
+    <t>L300</t>
   </si>
 </sst>
 </file>
@@ -404,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -429,327 +453,297 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="C2">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>180</v>
+        <v>25000</v>
       </c>
       <c r="G2">
+        <v>0.85</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>950</v>
+      </c>
+      <c r="C3">
+        <v>240</v>
+      </c>
+      <c r="D3">
+        <v>219</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>20000</v>
+      </c>
+      <c r="G3">
+        <v>0.85</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>600</v>
+      </c>
+      <c r="C4">
+        <v>240</v>
+      </c>
+      <c r="D4">
+        <v>208</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <v>20000</v>
+      </c>
+      <c r="G4">
+        <v>0.85</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>590</v>
+      </c>
+      <c r="C5">
+        <v>235</v>
+      </c>
+      <c r="D5">
+        <v>248</v>
+      </c>
+      <c r="E5">
+        <v>34.36</v>
+      </c>
+      <c r="F5">
+        <v>18600</v>
+      </c>
+      <c r="G5">
+        <v>0.85</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>650</v>
+      </c>
+      <c r="C6">
+        <v>240</v>
+      </c>
+      <c r="D6">
+        <v>192</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>18000</v>
+      </c>
+      <c r="G6">
+        <v>0.85</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>640</v>
+      </c>
+      <c r="C7">
+        <v>235</v>
+      </c>
+      <c r="D7">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>15000</v>
+      </c>
+      <c r="G7">
+        <v>0.85</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>500</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
         <v>15</v>
       </c>
-      <c r="C3">
-        <v>5000</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>500</v>
-      </c>
-      <c r="F3">
-        <v>200</v>
-      </c>
-      <c r="G3">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
+      <c r="F8">
         <v>8000</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>700</v>
-      </c>
-      <c r="F4">
-        <v>220</v>
-      </c>
-      <c r="G4">
+      <c r="G8">
+        <v>0.85</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>450</v>
+      </c>
+      <c r="C9">
+        <v>190</v>
+      </c>
+      <c r="D9">
+        <v>164</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>7000</v>
+      </c>
+      <c r="G9">
+        <v>0.85</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>420</v>
+      </c>
+      <c r="C10">
+        <v>185</v>
+      </c>
+      <c r="D10">
+        <v>154</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>6000</v>
+      </c>
+      <c r="G10">
+        <v>0.85</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>330</v>
+      </c>
+      <c r="C11">
+        <v>175</v>
+      </c>
+      <c r="D11">
+        <v>173</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>3000</v>
+      </c>
+      <c r="G11">
+        <v>0.85</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
         <v>240</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <v>15000</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>900</v>
-      </c>
-      <c r="F5">
-        <v>240</v>
-      </c>
-      <c r="G5">
-        <v>250</v>
+      <c r="C12">
+        <v>160</v>
+      </c>
+      <c r="D12">
+        <v>99</v>
+      </c>
+      <c r="E12">
+        <v>3.8</v>
+      </c>
+      <c r="F12">
+        <v>1500</v>
+      </c>
+      <c r="G12">
+        <v>0.85</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070E3D72CCA08644087C9FCADB1718278" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1cc8d91cc763930dc5d15b577ed7a101">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0886a85-e68e-4b42-8edb-c639a7945b69" xmlns:ns3="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6db848d96a87503e65ee1d4dfcdbf9d1" ns2:_="" ns3:_="">
-    <xsd:import namespace="b0886a85-e68e-4b42-8edb-c639a7945b69"/>
-    <xsd:import namespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b0886a85-e68e-4b42-8edb-c639a7945b69" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d90de106-bb39-41f4-915c-b71cc21c8f62" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cbd141ff-a5ff-442b-83f9-b2cf40ba1a7d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d44dd7a7-1c38-4d96-9b4d-61cfd733981b">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0886a85-e68e-4b42-8edb-c639a7945b69">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24D4AD04-4C36-4B63-8AAB-D3BCEDBE65D6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08BD9DD0-813B-4C15-9967-09ED91497EC5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E829B677-1520-4805-8F08-F8100DE78CF2}"/>
 </file>
--- a/data/master_armada.xlsx
+++ b/data/master_armada.xlsx
@@ -14,63 +14,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Jenis_Armada</t>
   </si>
   <si>
+    <t>Max_Volume_m3</t>
+  </si>
+  <si>
+    <t>Max_Tonase_Kg</t>
+  </si>
+  <si>
+    <t>Safety_Factor</t>
+  </si>
+  <si>
     <t>Length_cm</t>
   </si>
   <si>
+    <t>Height_cm</t>
+  </si>
+  <si>
     <t>Width_cm</t>
   </si>
   <si>
-    <t>Height_cm</t>
-  </si>
-  <si>
-    <t>Max_Volume_m3</t>
-  </si>
-  <si>
-    <t>Max_Tonase_Kg</t>
-  </si>
-  <si>
-    <t>Safety_Factor</t>
-  </si>
-  <si>
-    <t>is_active</t>
-  </si>
-  <si>
-    <t>BUILD UP</t>
-  </si>
-  <si>
-    <t>BUILD UP 20</t>
-  </si>
-  <si>
-    <t>FUSO (SUMATERA)</t>
-  </si>
-  <si>
-    <t>CONTAINER 20</t>
-  </si>
-  <si>
-    <t>TRONTON</t>
-  </si>
-  <si>
-    <t>ENGKEL</t>
-  </si>
-  <si>
-    <t>CDD LONG</t>
-  </si>
-  <si>
-    <t>DUTRO</t>
-  </si>
-  <si>
-    <t>CDD</t>
+    <t>Engkel</t>
   </si>
   <si>
     <t>CDE</t>
   </si>
   <si>
-    <t>L300</t>
+    <t>Fuso</t>
+  </si>
+  <si>
+    <t>Tronton</t>
   </si>
 </sst>
 </file>
@@ -428,10 +404,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,297 +429,327 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>2500</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>300</v>
+      </c>
+      <c r="F2">
+        <v>180</v>
+      </c>
+      <c r="G2">
+        <v>200</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>950</v>
-      </c>
-      <c r="C2">
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>500</v>
+      </c>
+      <c r="F3">
+        <v>200</v>
+      </c>
+      <c r="G3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>8000</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>700</v>
+      </c>
+      <c r="F4">
+        <v>220</v>
+      </c>
+      <c r="G4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>15000</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>900</v>
+      </c>
+      <c r="F5">
+        <v>240</v>
+      </c>
+      <c r="G5">
         <v>250</v>
-      </c>
-      <c r="D2">
-        <v>210</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>25000</v>
-      </c>
-      <c r="G2">
-        <v>0.85</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>950</v>
-      </c>
-      <c r="C3">
-        <v>240</v>
-      </c>
-      <c r="D3">
-        <v>219</v>
-      </c>
-      <c r="E3">
-        <v>50</v>
-      </c>
-      <c r="F3">
-        <v>20000</v>
-      </c>
-      <c r="G3">
-        <v>0.85</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>600</v>
-      </c>
-      <c r="C4">
-        <v>240</v>
-      </c>
-      <c r="D4">
-        <v>208</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>20000</v>
-      </c>
-      <c r="G4">
-        <v>0.85</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>590</v>
-      </c>
-      <c r="C5">
-        <v>235</v>
-      </c>
-      <c r="D5">
-        <v>248</v>
-      </c>
-      <c r="E5">
-        <v>34.36</v>
-      </c>
-      <c r="F5">
-        <v>18600</v>
-      </c>
-      <c r="G5">
-        <v>0.85</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>650</v>
-      </c>
-      <c r="C6">
-        <v>240</v>
-      </c>
-      <c r="D6">
-        <v>192</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>18000</v>
-      </c>
-      <c r="G6">
-        <v>0.85</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>640</v>
-      </c>
-      <c r="C7">
-        <v>235</v>
-      </c>
-      <c r="D7">
-        <v>200</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>15000</v>
-      </c>
-      <c r="G7">
-        <v>0.85</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>500</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>8000</v>
-      </c>
-      <c r="G8">
-        <v>0.85</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>450</v>
-      </c>
-      <c r="C9">
-        <v>190</v>
-      </c>
-      <c r="D9">
-        <v>164</v>
-      </c>
-      <c r="E9">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>7000</v>
-      </c>
-      <c r="G9">
-        <v>0.85</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>420</v>
-      </c>
-      <c r="C10">
-        <v>185</v>
-      </c>
-      <c r="D10">
-        <v>154</v>
-      </c>
-      <c r="E10">
-        <v>12</v>
-      </c>
-      <c r="F10">
-        <v>6000</v>
-      </c>
-      <c r="G10">
-        <v>0.85</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>330</v>
-      </c>
-      <c r="C11">
-        <v>175</v>
-      </c>
-      <c r="D11">
-        <v>173</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>3000</v>
-      </c>
-      <c r="G11">
-        <v>0.85</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>240</v>
-      </c>
-      <c r="C12">
-        <v>160</v>
-      </c>
-      <c r="D12">
-        <v>99</v>
-      </c>
-      <c r="E12">
-        <v>3.8</v>
-      </c>
-      <c r="F12">
-        <v>1500</v>
-      </c>
-      <c r="G12">
-        <v>0.85</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070E3D72CCA08644087C9FCADB1718278" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1cc8d91cc763930dc5d15b577ed7a101">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0886a85-e68e-4b42-8edb-c639a7945b69" xmlns:ns3="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6db848d96a87503e65ee1d4dfcdbf9d1" ns2:_="" ns3:_="">
+    <xsd:import namespace="b0886a85-e68e-4b42-8edb-c639a7945b69"/>
+    <xsd:import namespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b0886a85-e68e-4b42-8edb-c639a7945b69" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d90de106-bb39-41f4-915c-b71cc21c8f62" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cbd141ff-a5ff-442b-83f9-b2cf40ba1a7d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d44dd7a7-1c38-4d96-9b4d-61cfd733981b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0886a85-e68e-4b42-8edb-c639a7945b69">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d44dd7a7-1c38-4d96-9b4d-61cfd733981b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24D4AD04-4C36-4B63-8AAB-D3BCEDBE65D6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08BD9DD0-813B-4C15-9967-09ED91497EC5}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E829B677-1520-4805-8F08-F8100DE78CF2}"/>
 </file>